--- a/artfynd/A 51177-2024 artfynd.xlsx
+++ b/artfynd/A 51177-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R3" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R4" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 51177-2024 artfynd.xlsx
+++ b/artfynd/A 51177-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R3" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R4" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 51177-2024 artfynd.xlsx
+++ b/artfynd/A 51177-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121747235</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R3" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>90742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R4" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 51177-2024 artfynd.xlsx
+++ b/artfynd/A 51177-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121747235</v>
       </c>
       <c r="B2" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121793765</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121792902</v>
       </c>
       <c r="B4" t="n">
-        <v>90742</v>
+        <v>90744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51177-2024 artfynd.xlsx
+++ b/artfynd/A 51177-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121747235</v>
       </c>
       <c r="B2" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>90745</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R3" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B4" t="n">
-        <v>90744</v>
+        <v>98140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R4" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 51177-2024 artfynd.xlsx
+++ b/artfynd/A 51177-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121747235</v>
       </c>
       <c r="B2" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B3" t="n">
-        <v>90745</v>
+        <v>98149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R3" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B4" t="n">
-        <v>98140</v>
+        <v>90754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R4" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 51177-2024 artfynd.xlsx
+++ b/artfynd/A 51177-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121747235</v>
       </c>
       <c r="B2" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B3" t="n">
-        <v>98149</v>
+        <v>90761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R3" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B4" t="n">
-        <v>90754</v>
+        <v>98157</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R4" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 51177-2024 artfynd.xlsx
+++ b/artfynd/A 51177-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>121792902</v>
       </c>
       <c r="B3" t="n">
-        <v>90761</v>
+        <v>90763</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121793765</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51177-2024 artfynd.xlsx
+++ b/artfynd/A 51177-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792902</v>
+        <v>121793765</v>
       </c>
       <c r="B3" t="n">
-        <v>90763</v>
+        <v>98159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533320</v>
+        <v>533234</v>
       </c>
       <c r="R3" t="n">
-        <v>6332395</v>
+        <v>6332386</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121793765</v>
+        <v>121792902</v>
       </c>
       <c r="B4" t="n">
-        <v>98159</v>
+        <v>90763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533234</v>
+        <v>533320</v>
       </c>
       <c r="R4" t="n">
-        <v>6332386</v>
+        <v>6332395</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
